--- a/site/free-list/first-tuesday-list-2026-11-03.xlsx
+++ b/site/free-list/first-tuesday-list-2026-11-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov 3, 2026 sale" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nov 3, 2026 sale" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nov 3, 2026 sale'!$A$4:$P$799</definedName>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -326,13 +326,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/site/free-list/first-tuesday-list-2026-11-03.xlsx
+++ b/site/free-list/first-tuesday-list-2026-11-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nov 3, 2026 sale" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov 3, 2026 sale" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nov 3, 2026 sale'!$A$4:$P$799</definedName>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -326,13 +326,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/site/free-list/first-tuesday-list-2026-11-03.xlsx
+++ b/site/free-list/first-tuesday-list-2026-11-03.xlsx
@@ -661,7 +661,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>795 properties · free list from First Tuesday List · built 2026-10-25 · https://firsttuesdaylist.com/map</t>
+          <t>795 properties · free list from First Tuesday List · built 2026-10-26 · https://firsttuesdaylist.com/map</t>
         </is>
       </c>
     </row>
@@ -68404,7 +68404,7 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-25 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
+          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-26 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
         </is>
       </c>
     </row>

--- a/site/free-list/first-tuesday-list-2026-11-03.xlsx
+++ b/site/free-list/first-tuesday-list-2026-11-03.xlsx
@@ -661,7 +661,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>795 properties · free list from First Tuesday List · built 2026-10-26 · https://firsttuesdaylist.com/map</t>
+          <t>795 properties · free list from First Tuesday List · built 2026-10-27 · https://firsttuesdaylist.com/map</t>
         </is>
       </c>
     </row>
@@ -68404,7 +68404,7 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-26 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
+          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-27 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
         </is>
       </c>
     </row>

--- a/site/free-list/first-tuesday-list-2026-11-03.xlsx
+++ b/site/free-list/first-tuesday-list-2026-11-03.xlsx
@@ -661,7 +661,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>795 properties · free list from First Tuesday List · built 2026-10-27 · https://firsttuesdaylist.com/map</t>
+          <t>795 properties · free list from First Tuesday List · built 2026-10-31 · https://firsttuesdaylist.com/map</t>
         </is>
       </c>
     </row>
@@ -68404,7 +68404,7 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-27 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
+          <t>795 properties scheduled for the Nov 3, 2026 sale, built 2026-10-31 from notices filed with the Harris County Clerk. One row per property; filter by ZIP, type or flood zone with the arrows in the header.</t>
         </is>
       </c>
     </row>
